--- a/report_forms/040_software_package_availability_issue_report_form--report_forms.xlsx
+++ b/report_forms/040_software_package_availability_issue_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'availability_issue'}</t>
+          <t>availability_issue</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Availability Issue'}</t>
+          <t>Availability Issue</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'access_issue'}</t>
+          <t>access_issue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Access Issue'}</t>
+          <t>Access Issue</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'maintenance_issue'}</t>
+          <t>maintenance_issue</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Maintenance Issue'}</t>
+          <t>Maintenance Issue</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'assigned'}</t>
+          <t>assigned</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Assigned'}</t>
+          <t>Assigned</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'team_a'}</t>
+          <t>team_a</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Team A'}</t>
+          <t>Team A</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'team_b'}</t>
+          <t>team_b</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Team B'}</t>
+          <t>Team B</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'team_c'}</t>
+          <t>team_c</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Team C'}</t>
+          <t>Team C</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'ticket_1'}</t>
+          <t>ticket_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Ticket 1'}</t>
+          <t>Ticket 1</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'ticket_2'}</t>
+          <t>ticket_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Ticket 2'}</t>
+          <t>Ticket 2</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'ticket_3'}</t>
+          <t>ticket_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Ticket 3'}</t>
+          <t>Ticket 3</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'package_1'}</t>
+          <t>package_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Package 1'}</t>
+          <t>Package 1</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'package_2'}</t>
+          <t>package_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Package 2'}</t>
+          <t>Package 2</t>
         </is>
       </c>
     </row>
